--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H528"/>
+  <dimension ref="A1:H531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>396.94</v>
+        <v>391.36</v>
       </c>
       <c r="C527" t="n">
         <v>368.13</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>394.98</v>
+        <v>388.65</v>
       </c>
       <c r="C528" t="n">
         <v>371.19</v>
@@ -16280,6 +16280,96 @@
       <c r="H528" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>391.36</v>
+      </c>
+      <c r="C529" t="n">
+        <v>372.04</v>
+      </c>
+      <c r="D529" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="E529" t="n">
+        <v>384.82</v>
+      </c>
+      <c r="F529" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="G529" t="n">
+        <v>388.82</v>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="C530" t="n">
+        <v>372.88</v>
+      </c>
+      <c r="D530" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="E530" t="n">
+        <v>385.68</v>
+      </c>
+      <c r="F530" t="n">
+        <v>384.74</v>
+      </c>
+      <c r="G530" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>397.06</v>
+      </c>
+      <c r="C531" t="n">
+        <v>373.32</v>
+      </c>
+      <c r="D531" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="E531" t="n">
+        <v>386.04</v>
+      </c>
+      <c r="F531" t="n">
+        <v>385.03</v>
+      </c>
+      <c r="G531" t="n">
+        <v>389.58</v>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16294,7 +16384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22337,6 +22427,46 @@
       </c>
       <c r="B604" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -22505,28 +22635,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01705036962978954</v>
+        <v>-0.0191441821157456</v>
       </c>
       <c r="J2" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L2" t="n">
-        <v>5.093534748845663e-05</v>
+        <v>6.371495188783882e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>15.34697592675197</v>
+        <v>15.46590503280819</v>
       </c>
       <c r="N2" t="n">
-        <v>359.748417950704</v>
+        <v>364.7714812493541</v>
       </c>
       <c r="O2" t="n">
-        <v>18.96703503320179</v>
+        <v>19.09899162912414</v>
       </c>
       <c r="P2" t="n">
-        <v>425.8560700605503</v>
+        <v>426.2177564305573</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22583,28 +22713,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02714582445549264</v>
+        <v>0.02875191849895721</v>
       </c>
       <c r="J3" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K3" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004108641443866468</v>
+        <v>0.004654777732403192</v>
       </c>
       <c r="M3" t="n">
-        <v>2.830191873378888</v>
+        <v>2.82272972597251</v>
       </c>
       <c r="N3" t="n">
-        <v>11.25880986159691</v>
+        <v>11.21049320199183</v>
       </c>
       <c r="O3" t="n">
-        <v>3.355415005866921</v>
+        <v>3.348207461014301</v>
       </c>
       <c r="P3" t="n">
-        <v>370.4370420387437</v>
+        <v>370.4209829559826</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22661,28 +22791,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04681622887129586</v>
+        <v>0.0452759763211277</v>
       </c>
       <c r="J4" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K4" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008112436292314618</v>
+        <v>0.007674214364639664</v>
       </c>
       <c r="M4" t="n">
-        <v>3.358278805098591</v>
+        <v>3.347417847866927</v>
       </c>
       <c r="N4" t="n">
-        <v>16.89182960465902</v>
+        <v>16.81017647961832</v>
       </c>
       <c r="O4" t="n">
-        <v>4.109967105058023</v>
+        <v>4.100021521848186</v>
       </c>
       <c r="P4" t="n">
-        <v>380.5769735163282</v>
+        <v>380.592370494794</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22739,28 +22869,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05506601864174972</v>
+        <v>0.05605947102957122</v>
       </c>
       <c r="J5" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01854925297030663</v>
+        <v>0.01942173049734675</v>
       </c>
       <c r="M5" t="n">
-        <v>2.572331347649226</v>
+        <v>2.563373204189317</v>
       </c>
       <c r="N5" t="n">
-        <v>10.1130494677879</v>
+        <v>10.06256286068212</v>
       </c>
       <c r="O5" t="n">
-        <v>3.180102115937144</v>
+        <v>3.172154293328449</v>
       </c>
       <c r="P5" t="n">
-        <v>383.0542238213946</v>
+        <v>383.0442897893575</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22817,28 +22947,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04234545001163195</v>
+        <v>-0.0404860501832434</v>
       </c>
       <c r="J6" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K6" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01125803904932732</v>
+        <v>0.01040159036680099</v>
       </c>
       <c r="M6" t="n">
-        <v>2.46071109743808</v>
+        <v>2.457091714959465</v>
       </c>
       <c r="N6" t="n">
-        <v>9.926734596933166</v>
+        <v>9.889773255032067</v>
       </c>
       <c r="O6" t="n">
-        <v>3.150672086544895</v>
+        <v>3.144800988144093</v>
       </c>
       <c r="P6" t="n">
-        <v>383.9704145787668</v>
+        <v>383.9518237715367</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -22895,28 +23025,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1006838861156645</v>
+        <v>-0.09512099342615697</v>
       </c>
       <c r="J7" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="K7" t="n">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06552392259971462</v>
+        <v>0.05854259915033178</v>
       </c>
       <c r="M7" t="n">
-        <v>2.39210039962747</v>
+        <v>2.409907482498925</v>
       </c>
       <c r="N7" t="n">
-        <v>9.112990753192301</v>
+        <v>9.227789997947102</v>
       </c>
       <c r="O7" t="n">
-        <v>3.01877305427094</v>
+        <v>3.037727768900153</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4566687604496</v>
+        <v>386.4010522716566</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22954,7 +23084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H528"/>
+  <dimension ref="A1:H531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45057,7 +45187,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>-34.98528258200343,173.4479402703837</t>
+          <t>-34.98531543942552,173.44789396834747</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -45099,7 +45229,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>-34.985294123322156,173.44792400659026</t>
+          <t>-34.98533139705607,173.44787148114443</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -45130,6 +45260,132 @@
       <c r="H528" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>-34.98531543942552,173.44789396834747</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>-34.9859656887819,173.44829521194924</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>-34.98624263728536,173.44907531562683</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-34.98629276651424,173.44991627703874</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-34.98625175302626,173.45076448339037</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-34.9860256730063,173.45157244215554</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>-34.98528941258008,173.44793064487382</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>-34.98595980307432,173.44830100512277</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>-34.98623545227907,173.44907822899157</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-34.98628501622033,173.44991660020867</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>-34.98624686518959,173.45076346265708</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>-34.986022285617004,173.4515712939112</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>-34.98528187539201,173.44794126612598</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>-34.98595672008451,173.4483040396419</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>-34.986233228348546,173.4490791307472</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-34.986281771911244,173.44991673548907</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-34.986244287966606,173.45076292445233</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-34.98601907193994,173.45157020455127</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H531"/>
+  <dimension ref="A1:H535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16370,6 +16370,126 @@
       <c r="H531" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>401.61</v>
+      </c>
+      <c r="C532" t="n">
+        <v>373.69</v>
+      </c>
+      <c r="D532" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="E532" t="n">
+        <v>386.62</v>
+      </c>
+      <c r="F532" t="n">
+        <v>386.15</v>
+      </c>
+      <c r="G532" t="n">
+        <v>390.67</v>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>406.17</v>
+      </c>
+      <c r="C533" t="n">
+        <v>373.53</v>
+      </c>
+      <c r="D533" t="n">
+        <v>381.69</v>
+      </c>
+      <c r="E533" t="n">
+        <v>386.69</v>
+      </c>
+      <c r="F533" t="n">
+        <v>385.92</v>
+      </c>
+      <c r="G533" t="n">
+        <v>390.4</v>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>410.36</v>
+      </c>
+      <c r="C534" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="D534" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="E534" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="F534" t="n">
+        <v>385.96</v>
+      </c>
+      <c r="G534" t="n">
+        <v>390.44</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>412.99</v>
+      </c>
+      <c r="C535" t="n">
+        <v>373.76</v>
+      </c>
+      <c r="D535" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="E535" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="F535" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="G535" t="n">
+        <v>390.41</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16384,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B608"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22467,6 +22587,46 @@
       </c>
       <c r="B608" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -22635,28 +22795,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0191441821157456</v>
+        <v>-0.0430759536918856</v>
       </c>
       <c r="J2" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K2" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L2" t="n">
-        <v>6.371495188783882e-05</v>
+        <v>0.0003252873296387682</v>
       </c>
       <c r="M2" t="n">
-        <v>15.46590503280819</v>
+        <v>15.48575761355083</v>
       </c>
       <c r="N2" t="n">
-        <v>364.7714812493541</v>
+        <v>364.5292578746032</v>
       </c>
       <c r="O2" t="n">
-        <v>19.09899162912414</v>
+        <v>19.09264931523656</v>
       </c>
       <c r="P2" t="n">
-        <v>426.2177564305573</v>
+        <v>426.4578168959425</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22713,28 +22873,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02875191849895721</v>
+        <v>0.03204481497081239</v>
       </c>
       <c r="J3" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K3" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004654777732403192</v>
+        <v>0.005841835505356774</v>
       </c>
       <c r="M3" t="n">
-        <v>2.82272972597251</v>
+        <v>2.819217755764219</v>
       </c>
       <c r="N3" t="n">
-        <v>11.21049320199183</v>
+        <v>11.17101732848503</v>
       </c>
       <c r="O3" t="n">
-        <v>3.348207461014301</v>
+        <v>3.342307186433502</v>
       </c>
       <c r="P3" t="n">
-        <v>370.4209829559826</v>
+        <v>370.3879405790991</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22791,28 +22951,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0452759763211277</v>
+        <v>0.04518276542374209</v>
       </c>
       <c r="J4" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K4" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007674214364639664</v>
+        <v>0.007761035959748974</v>
       </c>
       <c r="M4" t="n">
-        <v>3.347417847866927</v>
+        <v>3.323642344884448</v>
       </c>
       <c r="N4" t="n">
-        <v>16.81017647961832</v>
+        <v>16.68450121740057</v>
       </c>
       <c r="O4" t="n">
-        <v>4.100021521848186</v>
+        <v>4.084666598071448</v>
       </c>
       <c r="P4" t="n">
-        <v>380.592370494794</v>
+        <v>380.5933038856517</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22869,28 +23029,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05605947102957122</v>
+        <v>0.05896122878805525</v>
       </c>
       <c r="J5" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K5" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01942173049734675</v>
+        <v>0.02169379151543072</v>
       </c>
       <c r="M5" t="n">
-        <v>2.563373204189317</v>
+        <v>2.560379059079134</v>
       </c>
       <c r="N5" t="n">
-        <v>10.06256286068212</v>
+        <v>10.0217468605034</v>
       </c>
       <c r="O5" t="n">
-        <v>3.172154293328449</v>
+        <v>3.165714273351813</v>
       </c>
       <c r="P5" t="n">
-        <v>383.0442897893575</v>
+        <v>383.0151713455675</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -22947,28 +23107,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0404860501832434</v>
+        <v>-0.03614971049118859</v>
       </c>
       <c r="J6" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K6" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01040159036680099</v>
+        <v>0.00837335821712859</v>
       </c>
       <c r="M6" t="n">
-        <v>2.457091714959465</v>
+        <v>2.462784753017915</v>
       </c>
       <c r="N6" t="n">
-        <v>9.889773255032067</v>
+        <v>9.893026942428195</v>
       </c>
       <c r="O6" t="n">
-        <v>3.144800988144093</v>
+        <v>3.145318257732943</v>
       </c>
       <c r="P6" t="n">
-        <v>383.9518237715367</v>
+        <v>383.9083109065439</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23025,28 +23185,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.09512099342615697</v>
+        <v>-0.08623416577292776</v>
       </c>
       <c r="J7" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="K7" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05854259915033178</v>
+        <v>0.04773780451919507</v>
       </c>
       <c r="M7" t="n">
-        <v>2.409907482498925</v>
+        <v>2.443378783058522</v>
       </c>
       <c r="N7" t="n">
-        <v>9.227789997947102</v>
+        <v>9.482522102652855</v>
       </c>
       <c r="O7" t="n">
-        <v>3.037727768900153</v>
+        <v>3.079370406861256</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4010522716566</v>
+        <v>386.3118809416406</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23084,7 +23244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H531"/>
+  <dimension ref="A1:H535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45389,6 +45549,174 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>-34.98525508303635,173.44797902134255</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>-34.985954127570295,173.4483065913965</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>-34.98622612887794,173.4490820094284</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-34.98627654496884,173.44991695344083</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-34.986234334553714,173.4507608458687</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>-34.98600960462102,173.45156699535633</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>-34.985228231784646,173.44801685951285</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>-34.985955248657525,173.44830548793507</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>-34.986225444591604,173.4490822868916</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-34.98627591413096,173.44991697974535</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>-34.98623637855815,173.45076127272065</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>-34.98601194973672,173.45156779029443</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>-34.9852035592426,173.44805162745894</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>-34.98595426770621,173.44830645346377</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>-34.98622570119899,173.4490821828429</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-34.98627492281429,173.44991702108103</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>-34.98623602307911,173.45076119848554</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>-34.98601160231217,173.45156767252584</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>-34.98518807265387,173.44807345076524</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>-34.98595363709464,173.44830707416085</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>-34.986222536374704,173.44908346611024</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-34.986274832694605,173.4499170248388</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>-34.98623229054926,173.45076041901677</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>-34.98601186288058,173.4515677608523</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0039/nzd0039.xlsx
+++ b/data/nzd0039/nzd0039.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H535"/>
+  <dimension ref="A1:H537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16488,6 +16488,66 @@
         <v>390.41</v>
       </c>
       <c r="H535" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>415.01</v>
+      </c>
+      <c r="C536" t="n">
+        <v>373.95</v>
+      </c>
+      <c r="D536" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="E536" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="F536" t="n">
+        <v>387.15</v>
+      </c>
+      <c r="G536" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>418.56</v>
+      </c>
+      <c r="C537" t="n">
+        <v>374.24</v>
+      </c>
+      <c r="D537" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="E537" t="n">
+        <v>387.56</v>
+      </c>
+      <c r="F537" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="G537" t="n">
+        <v>390.97</v>
+      </c>
+      <c r="H537" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16504,7 +16564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22627,6 +22687,26 @@
       </c>
       <c r="B612" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -22795,28 +22875,28 @@
         <v>0.0214</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0430759536918856</v>
+        <v>-0.04873979416324568</v>
       </c>
       <c r="J2" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K2" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003252873296387682</v>
+        <v>0.0004193098743221491</v>
       </c>
       <c r="M2" t="n">
-        <v>15.48575761355083</v>
+        <v>15.45968810516407</v>
       </c>
       <c r="N2" t="n">
-        <v>364.5292578746032</v>
+        <v>363.4474774212761</v>
       </c>
       <c r="O2" t="n">
-        <v>19.09264931523656</v>
+        <v>19.06429850325671</v>
       </c>
       <c r="P2" t="n">
-        <v>426.4578168959425</v>
+        <v>426.5149162919555</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22873,28 +22953,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03204481497081239</v>
+        <v>0.03393792788877857</v>
       </c>
       <c r="J3" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K3" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005841835505356774</v>
+        <v>0.006580567364880441</v>
       </c>
       <c r="M3" t="n">
-        <v>2.819217755764219</v>
+        <v>2.818768446723058</v>
       </c>
       <c r="N3" t="n">
-        <v>11.17101732848503</v>
+        <v>11.15915901387108</v>
       </c>
       <c r="O3" t="n">
-        <v>3.342307186433502</v>
+        <v>3.340532744020192</v>
       </c>
       <c r="P3" t="n">
-        <v>370.3879405790991</v>
+        <v>370.3688478302496</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22951,28 +23031,28 @@
         <v>0.1806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04518276542374209</v>
+        <v>0.04605966839859581</v>
       </c>
       <c r="J4" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K4" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007761035959748974</v>
+        <v>0.008121299331087739</v>
       </c>
       <c r="M4" t="n">
-        <v>3.323642344884448</v>
+        <v>3.316373897174353</v>
       </c>
       <c r="N4" t="n">
-        <v>16.68450121740057</v>
+        <v>16.62900139983882</v>
       </c>
       <c r="O4" t="n">
-        <v>4.084666598071448</v>
+        <v>4.077867261184309</v>
       </c>
       <c r="P4" t="n">
-        <v>380.5933038856517</v>
+        <v>380.5844574000244</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23029,28 +23109,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05896122878805525</v>
+        <v>0.06071473216316588</v>
       </c>
       <c r="J5" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K5" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02169379151543072</v>
+        <v>0.0230882669683643</v>
       </c>
       <c r="M5" t="n">
-        <v>2.560379059079134</v>
+        <v>2.56056781887129</v>
       </c>
       <c r="N5" t="n">
-        <v>10.0217468605034</v>
+        <v>10.01022101732506</v>
       </c>
       <c r="O5" t="n">
-        <v>3.165714273351813</v>
+        <v>3.163893332166093</v>
       </c>
       <c r="P5" t="n">
-        <v>383.0151713455675</v>
+        <v>382.9974848009358</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23107,28 +23187,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03614971049118859</v>
+        <v>-0.03318552856114651</v>
       </c>
       <c r="J6" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K6" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00837335821712859</v>
+        <v>0.007067935624584631</v>
       </c>
       <c r="M6" t="n">
-        <v>2.462784753017915</v>
+        <v>2.470242854652472</v>
       </c>
       <c r="N6" t="n">
-        <v>9.893026942428195</v>
+        <v>9.929238393907937</v>
       </c>
       <c r="O6" t="n">
-        <v>3.145318257732943</v>
+        <v>3.151069404806555</v>
       </c>
       <c r="P6" t="n">
-        <v>383.9083109065439</v>
+        <v>383.8784159853162</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -23185,28 +23265,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.08623416577292776</v>
+        <v>-0.08163713814445894</v>
       </c>
       <c r="J7" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K7" t="n">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04773780451919507</v>
+        <v>0.04255842809922472</v>
       </c>
       <c r="M7" t="n">
-        <v>2.443378783058522</v>
+        <v>2.4622177675116</v>
       </c>
       <c r="N7" t="n">
-        <v>9.482522102652855</v>
+        <v>9.622629278179389</v>
       </c>
       <c r="O7" t="n">
-        <v>3.079370406861256</v>
+        <v>3.102036311550751</v>
       </c>
       <c r="P7" t="n">
-        <v>386.3118809416406</v>
+        <v>386.2655207132103</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -23244,7 +23324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H535"/>
+  <dimension ref="A1:H537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45717,6 +45797,90 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>-34.98517617800893,173.44809021238657</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>-34.98595230580353,173.4483083845212</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>-34.98621586458296,173.4490861713762</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-34.98627366113854,173.44991707369005</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>-34.986225447577844,173.4507589899909</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>-34.98600873605964,173.4515667009348</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>-34.98515527404814,173.44811966967958</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>-34.98595027383287,173.44831038454484</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>-34.98621030475646,173.44908842576416</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-34.98626807371733,173.44991730667292</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>-34.986221448438705,173.45075815484603</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>-34.98600699893688,173.4515661120918</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
